--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:17</t>
+    <t xml:space="preserve">2026-09-09 21:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:02</t>
+    <t xml:space="preserve">2026-09-17 13:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_mean_a_2024.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:50</t>
+    <t xml:space="preserve">2026-10-05 18:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -578,7 +578,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>542072.62</v>
+        <v>542072.63</v>
       </c>
     </row>
     <row r="14">
